--- a/inventario reparaciones/componetes usados.xlsx
+++ b/inventario reparaciones/componetes usados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,270 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c1818</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>123</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>c1818</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C701039</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C701039</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>('C701039', 'CAJA ORG 4 / C8')</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C701039</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JORGE FUENTES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
